--- a/data/trans_dic/P1802_2016_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1802_2016_2023-Estudios-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,31; 19,6</t>
+          <t>14,27; 19,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,92; 23,33</t>
+          <t>15,74; 21,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,71; 26,15</t>
+          <t>20,46; 26,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,08; 22,47</t>
+          <t>18,37; 22,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,41; 22,35</t>
+          <t>18,41; 22,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,34; 22,17</t>
+          <t>17,74; 21,24</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,26; 15,44</t>
+          <t>12,1; 15,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,65; 49,28</t>
+          <t>12,95; 16,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,76; 19,25</t>
+          <t>15,61; 19,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,48; 17,24</t>
+          <t>16,19; 19,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,28; 16,53</t>
+          <t>14,26; 16,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,48; 33,18</t>
+          <t>14,87; 17,14</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,82; 17,17</t>
+          <t>10,73; 17,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,64; 18,63</t>
+          <t>12,2; 17,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,21; 20,13</t>
+          <t>13,6; 20,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,34; 23,89</t>
+          <t>18,1; 23,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,73; 17,08</t>
+          <t>12,8; 17,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,32; 20,25</t>
+          <t>15,85; 19,76</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,06; 15,57</t>
+          <t>13,21; 15,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,55; 38,86</t>
+          <t>13,98; 16,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,48; 20,22</t>
+          <t>17,56; 20,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,42; 18,96</t>
+          <t>17,78; 19,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,75; 17,58</t>
+          <t>15,76; 17,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,25; 30,33</t>
+          <t>16,14; 17,98</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>102947</t>
+          <t>106286</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154332</t>
+          <t>166267</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>257280</t>
+          <t>272553</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>107930; 147890</t>
+          <t>107633; 147165</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87142; 120110</t>
+          <t>91056; 126384</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>206010; 260063</t>
+          <t>203536; 259910</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136468; 169635</t>
+          <t>150878; 183208</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>322034; 390933</t>
+          <t>321985; 392970</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>232860; 281500</t>
+          <t>248346; 297424</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>554093</t>
+          <t>322741</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335249</t>
+          <t>381615</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>889342</t>
+          <t>704356</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>254516; 320635</t>
+          <t>251165; 317460</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>335510; 1128352</t>
+          <t>288735; 357407</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>313347; 382707</t>
+          <t>310408; 381529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>256738; 385486</t>
+          <t>351224; 414488</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>580270; 671879</t>
+          <t>579598; 672906</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>655332; 1501422</t>
+          <t>654228; 753857</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>99371</t>
+          <t>105006</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138432</t>
+          <t>150627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>237803</t>
+          <t>255634</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59192; 93889</t>
+          <t>58688; 93527</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81669; 120333</t>
+          <t>86721; 125589</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72518; 110541</t>
+          <t>74669; 111864</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121022; 157625</t>
+          <t>132871; 170207</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>139505; 187225</t>
+          <t>140275; 189336</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>213119; 264372</t>
+          <t>229061; 285500</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>756412</t>
+          <t>534034</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>628013</t>
+          <t>698510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1384425</t>
+          <t>1232543</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>440998; 526005</t>
+          <t>446321; 527049</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536592; 1340823</t>
+          <t>492011; 578747</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>617426; 714229</t>
+          <t>620237; 717566</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>526434; 691993</t>
+          <t>662408; 739156</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1088057; 1214968</t>
+          <t>1089302; 1218518</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1153834; 2154015</t>
+          <t>1168855; 1302175</t>
         </is>
       </c>
     </row>
